--- a/tests/excel-oracle/error-normalization/fixture.xlsx
+++ b/tests/excel-oracle/error-normalization/fixture.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93433CE-DD03-443E-B768-F7315CED3705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89E99E4-7038-4D4C-8E80-1EE3E6C9331F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F9B537CA-3367-4E1C-BA6D-90BB4FDC86C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5D72E456-DABF-4666-8507-847476F3BE9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
@@ -399,7 +399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22B47C8-D9B1-4202-90DF-B590C0889C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708CCFB0-DBC2-431F-8B38-C2F31D56158A}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
